--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0023.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0023.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>HP của kẻ địch bất bại không reset khi đối mặt với đội hình mới.</t>
+          <t>Kẻ địch bất bại sẽ không hồi phục HP khi đối mặt với đội hình mới.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HP của kẻ địch bất bại không reset khi đối mặt với đội hình mới.</t>
+          <t>Kẻ địch bất bại sẽ không hồi phục HP khi đối mặt với đội hình mới.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để kiếm Points Mod và nâng cấp Mô-đun Mở Rộng.</t>
+          <t>Hoàn thành nhiệm vụ để nhận Điểm Cải Tiến và nâng cấp Mô-đun Mở Rộng.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để kiếm Points Mod và nâng cấp Mô-đun Mở Rộng.</t>
+          <t>Hoàn thành nhiệm vụ để nhận Điểm Cải Tiến và nâng cấp Mô-đun Mở Rộng.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để kiếm Points Mod và nâng cấp Mô-đun Mở Rộng.</t>
+          <t>Hoàn thành nhiệm vụ để nhận Điểm Cải Tiến và nâng cấp Mô-đun Mở Rộng.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Vật liệu cần thiết để kích hoạt Bộ Tạo Lộ Trình được hiển thị tại đây.</t>
+          <t>Vật liệu cần thiết để kích hoạt Bộ Xây Dựng Lộ Trình được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vật liệu cần thiết để kích hoạt Bộ Tạo Lộ Trình được hiển thị tại đây.</t>
+          <t>Vật liệu cần thiết để kích hoạt Bộ Xây Dựng Lộ Trình được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Vật liệu cần thiết để kích hoạt Bộ Tạo Lộ Trình được hiển thị tại đây.</t>
+          <t>Vật liệu cần thiết để kích hoạt Bộ Xây Dựng Lộ Trình được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ có thể được thêm vào đội của bạn sau khi tuyển dụng.</t>
+          <t>Resonator Hỗ Trợ có thể được thêm vào đội của bạn sau khi chiêu mộ.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ có thể được thêm vào đội của bạn sau khi tuyển dụng.</t>
+          <t>Resonator Hỗ Trợ có thể được thêm vào đội của bạn sau khi chiêu mộ.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Resonators hỗ trợ có thể được thêm vào đội của bạn sau khi tuyển dụng.</t>
+          <t>Resonator Hỗ Trợ có thể được thêm vào đội của bạn sau khi chiêu mộ.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Xem các Resonator Hỗ Trợ khả dụng tại đây.</t>
+          <t>Xem Resonator Hỗ Trợ khả dụng tại đây.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Xem các Resonator Hỗ Trợ khả dụng tại đây.</t>
+          <t>Xem Resonator Hỗ Trợ khả dụng tại đây.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Xem các Resonator Hỗ Trợ khả dụng tại đây.</t>
+          <t>Xem Resonator Hỗ Trợ khả dụng tại đây.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Chọn một Resonator Hỗ Trợ để tham gia đội của bạn.</t>
+          <t>Chọn Resonator hỗ trợ để gia nhập đội của bạn</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Chọn một Resonator Hỗ Trợ để tham gia đội của bạn.</t>
+          <t>Chọn Resonator hỗ trợ để gia nhập đội của bạn</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Chọn một Resonator Hỗ Trợ để tham gia đội của bạn.</t>
+          <t>Chọn Resonator hỗ trợ để gia nhập đội của bạn</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Vào trang Đội hình và thêm Resonator Hỗ Trợ vào đội của bạn.</t>
+          <t>Vào trang Đội Hình và thêm Resonator Hỗ Trợ vào đội của cậu.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Vào trang Đội hình và thêm Resonator Hỗ Trợ vào đội của bạn.</t>
+          <t>Vào trang Đội Hình và thêm Resonator Hỗ Trợ vào đội của cậu.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Vào trang Đội hình và thêm Resonator Hỗ Trợ vào đội của bạn.</t>
+          <t>Vào trang Đội Hình và thêm Resonator Hỗ Trợ vào đội của cậu.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Bạn có thể thêm Resonator Hỗ Trợ vào đội của mình.</t>
+          <t>Cậu có thể thêm Resonator Hỗ Trợ vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Bạn có thể thêm Resonator Hỗ Trợ vào đội của mình.</t>
+          <t>Cậu có thể thêm Resonator Hỗ Trợ vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bạn có thể thêm Resonator Hỗ Trợ vào đội của mình.</t>
+          <t>Cậu có thể thêm Resonator Hỗ Trợ vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Cấp độ của Resonator Hỗ Trợ tăng theo SOL3 Giai đoạn của bạn.</t>
+          <t>Cấp độ của Resonator Hỗ Trợ sẽ tăng theo Giai Đoạn SOL3 của cậu.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Cấp độ của Resonator Hỗ Trợ tăng theo SOL3 Giai đoạn của bạn.</t>
+          <t>Cấp độ của Resonator Hỗ Trợ sẽ tăng theo Giai Đoạn SOL3 của cậu.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cấp độ của Resonator Hỗ Trợ tăng theo SOL3 Giai đoạn của bạn.</t>
+          <t>Cấp độ của Resonator Hỗ Trợ sẽ tăng theo Giai Đoạn SOL3 của cậu.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem Livery mới</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Trang Phục mới.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem Livery mới</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Trang Phục mới.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem Livery mới</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Trang Phục mới.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Dùng Mẫu Nhập để trang bị toàn bộ Livery</t>
+          <t>Dùng Import Preset để trang bị toàn bộ Livery.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Dùng Mẫu Nhập để trang bị toàn bộ Livery</t>
+          <t>Dùng Import Preset để trang bị toàn bộ Livery.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Dùng Mẫu Nhập để trang bị toàn bộ Livery</t>
+          <t>Dùng Import Preset để trang bị toàn bộ Livery.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem Livery bạn nhận được từ Lynae.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Trang Phục nhận được từ Lynae.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem Livery bạn nhận được từ Lynae.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Trang Phục nhận được từ Lynae.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để xem Livery bạn nhận được từ Lynae.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Trang Phục nhận được từ Lynae.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Place Electro Predator vào đây. Các Echoes ở phía bên phải Khu Triển Khai sẽ xuất hiện ở Hàng Sau.</t>
+          <t>Đặt Electro Predator vào đây. Các Echo ở bên phải Khu Triển Khai sẽ xuất hiện ở Hàng Sau.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Place Electro Predator vào đây. Các Echoes ở phía bên phải Khu Triển Khai sẽ xuất hiện ở Hàng Sau.</t>
+          <t>Đặt Electro Predator vào đây. Các Echo ở bên phải Khu Triển Khai sẽ xuất hiện ở Hàng Sau.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Place Electro Predator vào đây. Các Echoes ở phía bên phải Khu Triển Khai sẽ xuất hiện ở Hàng Sau.</t>
+          <t>Đặt Electro Predator vào đây. Các Echo ở bên phải Khu Triển Khai sẽ xuất hiện ở Hàng Sau.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để bắn Tia Quang Tử.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để bắn Photonic Beam.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để bắn Tia Quang Tử.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để bắn Photonic Beam.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} vào đây để bắn Tia Quang Tử.</t>
+          <t>Nhấn vào đây để bắn Tia Quang Tử.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Thu thập năng lượng để phóng Tia Quang Tử gây sát thương cho Voidworm.</t>
+          <t>Thu thập năng lượng để kích hoạt Tia Quang Tử, tấn công Voidworm</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Thu thập năng lượng để phóng Tia Quang Tử gây sát thương cho Voidworm.</t>
+          <t>Thu thập năng lượng để kích hoạt Tia Quang Tử, tấn công Voidworm</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Thu thập năng lượng để phóng Tia Quang Tử gây sát thương cho Voidworm.</t>
+          <t>Thu thập năng lượng để kích hoạt Tia Quang Tử, tấn công Voidworm</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>{0} Đến trang Đội Hình để chỉnh sửa đội.</t>
+          <t>Vào trang Đội để chỉnh đội hình.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{0} Đến trang Đội Hình để chỉnh sửa đội.</t>
+          <t>Vào trang Đội để chỉnh đội hình.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hãy vào trang Đội để chỉnh đội hình.</t>
+          <t>Vào trang Đội Hình để chỉnh sửa đội hình.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Hãy vào trang Đội để chỉnh đội hình.</t>
+          <t>Vào trang Đội Hình để chỉnh sửa đội hình.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Mở Rộng Bounce Nhảy</t>
+          <t>Chọn Mô-đun Mở Rộng Nhảy Bật</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Mở Rộng Bounce Nhảy</t>
+          <t>Chọn Mô-đun Mở Rộng Nhảy Bật</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Chọn Mô-đun Mở Rộng Bounce Nhảy</t>
+          <t>Chọn Mô-đun Mở Rộng Nhảy Bật</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=Chọn} để mở khóa Mô-đun Mở Rộng Bật Nhảy</t>
+          <t>Chọn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Select} để mở khóa Mô-đun Mở Rộng Nhảy Bật.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=Chọn} để mở khóa Mô-đun Mở Rộng Bật Nhảy</t>
+          <t>Chọn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Select} để mở khóa Mô-đun Mở Rộng Nhảy Bật.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=Chọn} để mở khóa Mô-đun Mở Rộng Bật Nhảy</t>
+          <t>Chọn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Select} để mở khóa Mô-đun Mở Rộng Nhảy Bật.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Echoes của cậu đã thắng trận đấu vừa rồi.</t>
+          <t>Echo của cậu đã thắng trận đấu trước.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Echoes của cậu đã thắng trận đấu vừa rồi.</t>
+          <t>Echo của cậu đã thắng trận đấu trước.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Echoes của cậu đã thắng trận đấu vừa rồi.</t>
+          <t>Echo của cậu đã thắng trận đấu trước.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Năng lượng của cậu đã phục hồi. Triển khai thêm Echoes để đánh bại đối thủ.</t>
+          <t>Năng lượng của cậu đã hồi phục. Triệu hồi thêm Echo để đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Năng lượng của cậu đã phục hồi. Triển khai thêm Echoes để đánh bại đối thủ.</t>
+          <t>Năng lượng của cậu đã hồi phục. Triệu hồi thêm Echo để đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Năng lượng của cậu đã phục hồi. Triển khai thêm Echoes để đánh bại đối thủ.</t>
+          <t>Năng lượng của cậu đã hồi phục. Triệu hồi thêm Echo để đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Tiêu diệt kẻ địch và giành chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Tiêu diệt kẻ địch và giành chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch và giành chiến thắng.</t>
+          <t>Tiêu diệt kẻ địch và giành chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hoàn thành Trial để thêm Core Echo vào tay.</t>
+          <t>Hoàn thành Thử Thách để thêm Bản Sao Lõi vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hoàn thành Trial để thêm Core Echo vào tay.</t>
+          <t>Hoàn thành Thử Thách để thêm Bản Sao Lõi vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Hoàn thành Trial để thêm Core Echo vào tay.</t>
+          <t>Hoàn thành Thử Thách để thêm Bản Sao Lõi vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Bạn phải chọn Resonator Tactics và bộ bài trước khi đấu.</t>
+          <t>Cậu phải chọn Chiến Thuật Resonator và bộ bài trước khi đấu.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Bạn phải chọn Resonator Tactics và bộ bài trước khi đấu.</t>
+          <t>Cậu phải chọn Chiến Thuật Resonator và bộ bài trước khi đấu.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Bạn phải chọn Resonator Tactics và bộ bài trước khi đấu.</t>
+          <t>Cậu phải chọn Chiến Thuật Resonator và bộ bài trước khi đấu.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu thử thách</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu thử thách</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu thử thách</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu thách đấu</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu thách đấu</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để bắt đầu thách đấu</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thử thách, các avatar ở đây là những boss bạn sẽ đối đầu</t>
+          <t>Màn hình này hiển thị tiến độ thử thách, và những hình đại diện ở đây là các trùm bạn sẽ đối mặt.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thử thách, các avatar ở đây là những boss bạn sẽ đối đầu</t>
+          <t>Màn hình này hiển thị tiến độ thử thách, và những hình đại diện ở đây là các trùm bạn sẽ đối mặt.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Hiển thị tiến độ thử thách, các avatar ở đây là những boss bạn sẽ đối đầu</t>
+          <t>Màn hình này hiển thị tiến độ thử thách, và những hình đại diện ở đây là các trùm bạn sẽ đối mặt.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Xem điểm hiện tại và thời gian đã sử dụng trong trận đấu tại đây.</t>
+          <t>Xem điểm hiện tại và thời gian đã sử dụng trong trận đấu tại đây</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Xem điểm hiện tại và thời gian đã sử dụng trong trận đấu tại đây.</t>
+          <t>Xem điểm hiện tại và thời gian đã sử dụng trong trận đấu tại đây</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Xem điểm hiện tại và thời gian đã sử dụng trong trận đấu tại đây.</t>
+          <t>Xem điểm hiện tại và thời gian đã sử dụng trong trận đấu tại đây</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>HP của tay đua xe được hiển thị ở dưới. Mất hết HP sẽ thất bại thử thách</t>
+          <t>HP của tay đua xe hiện ở dưới đáy màn hình. Mất hết HP sẽ thất bại thử thách.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>HP của tay đua xe được hiển thị ở dưới. Mất hết HP sẽ thất bại thử thách</t>
+          <t>HP của tay đua xe hiện ở dưới đáy màn hình. Mất hết HP sẽ thất bại thử thách.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>HP của tay đua xe được hiển thị ở dưới. Mất hết HP sẽ thất bại thử thách</t>
+          <t>HP của tay đua xe hiện ở dưới đáy màn hình. Mất hết HP sẽ thất bại thử thách.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch Thủ lĩnh hoặc Boss sẽ nhận được Vật phẩm Hỗ trợ đặc biệt để người chơi lựa chọn</t>
+          <t>Tiêu diệt kẻ địch Elite hoặc Boss sẽ rơi ra các Vật Phẩm Hỗ Trợ đặc biệt để người lái xe lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch Thủ lĩnh hoặc Boss sẽ nhận được Vật phẩm Hỗ trợ đặc biệt để người chơi lựa chọn</t>
+          <t>Tiêu diệt kẻ địch Elite hoặc Boss sẽ rơi ra các Vật Phẩm Hỗ Trợ đặc biệt để người lái xe lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch Thủ lĩnh hoặc Boss sẽ nhận được Vật phẩm Hỗ trợ đặc biệt để người chơi lựa chọn</t>
+          <t>Tiêu diệt kẻ địch Elite hoặc Boss sẽ rơi ra các Vật Phẩm Hỗ Trợ đặc biệt để người lái xe lựa chọn.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Nâng cấp xe máy của bạn thêm tại đây</t>
+          <t>Nâng cấp xe máy của cậu tại đây</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>{0} để nâng cấp xe máy thêm</t>
+          <t>Nhấn {0} để nâng cấp xe máy thêm một bậc</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nâng cấp xe máy của bạn thêm tại đây</t>
+          <t>Nâng cấp xe máy của cậu tại đây</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chìa khóa Tin Cậy kiếm được từ thử thách có thể dùng để mở khóa thêm hiệu ứng tăng cường</t>
+          <t>Chìa Khóa Niềm Tin kiếm được từ các thử thách có thể dùng để mở khóa những hiệu ứng tăng cường bổ sung</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Chìa khóa Tin Cậy kiếm được từ thử thách có thể dùng để mở khóa thêm hiệu ứng tăng cường</t>
+          <t>Chìa Khóa Niềm Tin kiếm được từ các thử thách có thể dùng để mở khóa những hiệu ứng tăng cường bổ sung</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chìa khóa Tin Cậy kiếm được từ thử thách có thể dùng để mở khóa thêm hiệu ứng tăng cường</t>
+          <t>Chìa Khóa Niềm Tin kiếm được từ các thử thách có thể dùng để mở khóa những hiệu ứng tăng cường bổ sung</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Ngoài Vũ Khí Main, bạn có thể lắp đặt một Hỗ Trợ Droid lên xe máy</t>
+          <t>Ngoài Vũ Khí Chính, bạn có thể lắp thêm một Droid Hỗ Trợ lên xe máy của mình</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ngoài Vũ Khí Main, bạn có thể lắp đặt một Hỗ Trợ Droid lên xe máy</t>
+          <t>Ngoài Vũ Khí Chính, bạn có thể lắp thêm một Droid Hỗ Trợ lên xe máy của mình</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Ngoài Vũ Khí Main, bạn có thể lắp đặt một Hỗ Trợ Droid lên xe máy</t>
+          <t>Ngoài Vũ Khí Chính, bạn có thể lắp thêm một Droid Hỗ Trợ lên xe máy của mình</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Đã lưu tiến trình. Bạn sẽ tiếp tục từ đây khi vào lại</t>
+          <t>Đã lưu tiến trình. Lần sau vào, cậu sẽ tiếp tục từ đây</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Đã lưu tiến trình. Bạn sẽ tiếp tục từ đây khi vào lại</t>
+          <t>Đã lưu tiến trình. Lần sau vào, cậu sẽ tiếp tục từ đây</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Đã lưu tiến trình. Bạn sẽ tiếp tục từ đây khi vào lại</t>
+          <t>Đã lưu tiến trình. Lần sau vào, cậu sẽ tiếp tục từ đây</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem mô-đun xe mới mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem mô-đun xe máy mới mở khóa.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} {0} để xem mô-đun xe mới mở khóa</t>
+          <t>Nhấn {0} để xem mô-đun xe máy mới mở khóa.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem mô-đun xe mới mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem mô-đun xe máy mới mở khóa.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chọn mô-đun xe mới</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn mô-đun xe mới</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chọn mô-đun xe mới</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn mô-đun xe mới</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chọn mô-đun xe mới</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn mô-đun xe mới</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Mỗi mô-đun kỹ năng xe máy đều có hiệu ứng riêng biệt</t>
+          <t>Mỗi mô-đun kỹ năng của dân đua xe đều có hiệu ứng riêng biệt.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Mỗi mô-đun kỹ năng xe máy đều có hiệu ứng riêng biệt</t>
+          <t>Mỗi mô-đun kỹ năng của dân đua xe đều có hiệu ứng riêng biệt.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Mỗi mô-đun kỹ năng xe máy đều có hiệu ứng riêng biệt</t>
+          <t>Mỗi mô-đun kỹ năng của dân đua xe đều có hiệu ứng riêng biệt.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để đổi xe</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển đổi xe</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để đổi xe</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển đổi xe</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để đổi xe</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển đổi xe</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Kỹ năng của đối thủ sẽ không hiển thị cho đến khi được sử dụng một lần trong trận đấu</t>
+          <t>Kỹ năng của đối thủ sẽ vẫn là ẩn số cho đến khi họ sử dụng một lần trong trận đấu</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Kỹ năng của đối thủ sẽ không hiển thị cho đến khi được sử dụng một lần trong trận đấu</t>
+          <t>Kỹ năng của đối thủ sẽ vẫn là ẩn số cho đến khi họ sử dụng một lần trong trận đấu</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Kỹ năng của đối thủ sẽ không hiển thị cho đến khi được sử dụng một lần trong trận đấu</t>
+          <t>Kỹ năng của đối thủ sẽ vẫn là ẩn số cho đến khi họ sử dụng một lần trong trận đấu</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết kỹ năng của Rover</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết kỹ năng của Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để xem chi tiết kỹ năng của Rover</t>
+          <t>Nhấn {0} để xem chi tiết kỹ năng của Rover.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết kỹ năng của Rover</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết kỹ năng của Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Khi có hai lá bài giống nhau trên tay, bạn có thể đánh chúng theo cặp</t>
+          <t>Khi có hai lá bài giống nhau trên tay, cậu có thể đánh chúng theo cặp.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Khi có hai lá bài giống nhau trên tay, bạn có thể đánh chúng theo cặp</t>
+          <t>Khi có hai lá bài giống nhau trên tay, cậu có thể đánh chúng theo cặp.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi có hai lá bài giống nhau trên tay, bạn có thể đánh chúng theo cặp</t>
+          <t>Khi có hai lá bài giống nhau trên tay, cậu có thể đánh chúng theo cặp.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} nút để đánh tất cả các cặp trên tay</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để đánh tất cả các cặp bài trên tay.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} nút để đánh tất cả các cặp bài trên tay</t>
+          <t>Nhấn {0} để chơi tất cả các cặp bài trên tay</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} nút để đánh tất cả các cặp trên tay</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để đánh tất cả các cặp bài trên tay.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Khi rút được lá bài trùng với lá bài trên tay, bạn có thể đánh chúng theo cặp</t>
+          <t>Khi rút được lá bài trùng với lá đang có trên tay, cậu có thể đánh chúng thành một cặp.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>{0} Khi rút được lá bài trùng với lá đang có trên tay, bạn có thể đánh chúng theo cặp</t>
+          <t>Khi rút được lá bài trùng với lá bài đang có trên tay, bạn có thể đánh chúng theo cặp.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Khi rút được lá bài trùng với lá bài trên tay, bạn có thể đánh chúng theo cặp</t>
+          <t>Khi rút được lá bài trùng với lá đang có trên tay, cậu có thể đánh chúng thành một cặp.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Rút Thẻ Không Vương Miện tiêu hao 1 HP. Mất 2 HP đồng nghĩa với thất bại</t>
+          <t>Rút thẻ Crownless sẽ khiến ngươi mất 1 HP. Mất 2 HP đồng nghĩa với thất bại.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Rút Thẻ Không Vương Miện tiêu hao 1 HP. Mất 2 HP đồng nghĩa với thất bại</t>
+          <t>Rút thẻ Crownless sẽ khiến ngươi mất 1 HP. Mất 2 HP đồng nghĩa với thất bại.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Rút Thẻ Không Vương Miện tiêu hao 1 HP. Mất 2 HP đồng nghĩa với thất bại</t>
+          <t>Rút thẻ Crownless sẽ khiến ngươi mất 1 HP. Mất 2 HP đồng nghĩa với thất bại.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{0} để xem kỹ năng đã tiết lộ của đối thủ</t>
+          <t>Nhấn {0} để xem kỹ năng đã tiết lộ của đối thủ</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Thẻ Bất Kỳ biến thành thẻ ngẫu nhiên mỗi lượt</t>
+          <t>Thẻ Bất Định biến hình ngẫu nhiên mỗi lượt</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Thẻ Bất Kỳ biến thành thẻ ngẫu nhiên mỗi lượt</t>
+          <t>Thẻ Bất Định biến hình ngẫu nhiên mỗi lượt</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Thẻ Bất Kỳ biến thành thẻ ngẫu nhiên mỗi lượt</t>
+          <t>Thẻ Bất Định biến hình ngẫu nhiên mỗi lượt</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Xem tại đây để kiểm tra Wild Card đã biến thành gì.</t>
+          <t>Xem tại đây để biết Thẻ Hoang Dã đã biến thành gì</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Xem tại đây để kiểm tra Wild Card đã biến thành gì.</t>
+          <t>Xem tại đây để biết Thẻ Hoang Dã đã biến thành gì</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Xem tại đây để kiểm tra Wild Card đã biến thành gì.</t>
+          <t>Xem tại đây để biết Thẻ Hoang Dã đã biến thành gì</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết kỹ năng của Rover</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết kỹ năng của Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để xem chi tiết kỹ năng của Rover</t>
+          <t>Nhấn {0} để xem chi tiết kỹ năng của Rover.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết kỹ năng của Rover</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết kỹ năng của Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Vibe Level đã tăng. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem nội dung đã mở khóa</t>
+          <t>Tần Số Vui Vẻ tăng lên. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem nội dung đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Vibe Level đã tăng. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem nội dung đã mở khóa</t>
+          <t>Tần Số Vui Vẻ tăng lên. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem nội dung đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Vibe Level đã tăng. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem nội dung đã mở khóa</t>
+          <t>Tần Số Vui Vẻ tăng lên. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem nội dung đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Increase Vibe Level để mở khóa thêm nội dung</t>
+          <t>Nâng Cấp Độ Cảm Xúc để mở khóa thêm nội dung</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Increase Vibe Level để mở khóa thêm nội dung</t>
+          <t>Nâng Cấp Độ Cảm Xúc để mở khóa thêm nội dung</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Increase Vibe Level để mở khóa thêm nội dung</t>
+          <t>Nâng Cấp Độ Cảm Xúc để mở khóa thêm nội dung</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để bắt đầu Party Decor</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu Trang trí Bữa tiệc</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để bắt đầu Trang trí Đội</t>
+          <t>Nhấn {0} để bắt đầu Trang Trí Bữa Tiệc.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để bắt đầu Party Decor</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu Trang trí Bữa tiệc</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Trưng bày đồ trang trí để tăng Đồng Hồ Sôi Động</t>
+          <t>Trưng bày vật phẩm trang trí để tăng Đồng Hồ Sôi Động</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Trưng bày đồ trang trí để tăng Đồng Hồ Sôi Động</t>
+          <t>Trưng bày vật phẩm trang trí để tăng Đồng Hồ Sôi Động</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Trưng bày đồ trang trí để tăng Đồng Hồ Sôi Động</t>
+          <t>Trưng bày vật phẩm trang trí để tăng Đồng Hồ Sôi Động</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào trang trí để hiển thị hoặc chuyển đổi</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào vật trang trí để hiển thị hoặc thay đổi.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào trang trí để hiển thị hoặc chuyển đổi</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào vật trang trí để hiển thị hoặc thay đổi.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào trang trí để hiển thị hoặc chuyển đổi</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào vật trang trí để hiển thị hoặc thay đổi.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển sang khu vực khác để trang trí</t>
+          <t>Bạn có thể chuyển sang khu vực khác để trang trí.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển sang khu vực khác để trang trí</t>
+          <t>Bạn có thể chuyển sang khu vực khác để trang trí.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển sang khu vực khác để trang trí</t>
+          <t>Bạn có thể chuyển sang khu vực khác để trang trí.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Mở khóa Trang Trí Nhanh. Dùng để hiển thị nhanh đồ trang trí đã cài đặt sẵn</t>
+          <t>Tính năng Trang trí Nhanh đã mở khóa. Dùng để hiển thị nhanh các vật trang trí đã cài đặt trước</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Mở khóa Trang Trí Nhanh. Dùng để hiển thị nhanh đồ trang trí đã cài đặt sẵn</t>
+          <t>Tính năng Trang trí Nhanh đã mở khóa. Dùng để hiển thị nhanh các vật trang trí đã cài đặt trước</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Mở khóa Trang Trí Nhanh. Dùng để hiển thị nhanh đồ trang trí đã cài đặt sẵn</t>
+          <t>Tính năng Trang trí Nhanh đã mở khóa. Dùng để hiển thị nhanh các vật trang trí đã cài đặt trước</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để vào Shop Trang Trí và mở khóa thêm vật phẩm trang trí</t>
+          <t>Nhấn vào đây để vào Cửa Hàng Trang Trí và mở khóa thêm vật phẩm trang trí.</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để vào Shop Trang Trí và mở khóa thêm vật phẩm trang trí</t>
+          <t>Nhấn vào đây để vào Cửa Hàng Trang Trí và mở khóa thêm vật phẩm trang trí.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để vào Shop Trang Trí và mở khóa thêm vật phẩm trang trí</t>
+          <t>Nhấn vào đây để vào Cửa Hàng Trang Trí và mở khóa thêm vật phẩm trang trí.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem đơn đồ uống và hương vị ưa thích của bạn đồng hành</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem đơn đồ uống và hương vị yêu thích của bạn đồng hành.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem đơn đồ uống và hương vị ưa thích của bạn đồng hành</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem đơn đồ uống và hương vị yêu thích của bạn đồng hành.</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem đơn đồ uống và hương vị ưa thích của bạn đồng hành</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem đơn đồ uống và hương vị yêu thích của bạn đồng hành.</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Chọn nền thức uống đầu tiên.</t>
+          <t>Chọn loại rượu nền đầu tiên</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Chọn nền thức uống đầu tiên.</t>
+          <t>Chọn loại rượu nền đầu tiên</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Chọn nền thức uống đầu tiên.</t>
+          <t>Chọn loại rượu nền đầu tiên</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Nồng độ nguyên liệu đồ uống khác nhau tạo ra nhiều hương vị khác nhau</t>
+          <t>Nồng độ nền đồ uống khác nhau sẽ tạo ra hương vị đa dạng.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nồng độ nguyên liệu đồ uống khác nhau tạo ra nhiều hương vị khác nhau</t>
+          <t>Nồng độ nền đồ uống khác nhau sẽ tạo ra hương vị đa dạng.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nồng độ nguyên liệu đồ uống khác nhau tạo ra nhiều hương vị khác nhau</t>
+          <t>Nồng độ nền đồ uống khác nhau sẽ tạo ra hương vị đa dạng.</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Đánh giá về người bạn đồng hành của bạn có thể thay đổi tùy thuộc vào nguyên liệu bạn chọn cho đồ uống của họ</t>
+          <t>Đánh giá của bạn đồng hành có thể thay đổi tùy vào nguyên liệu cậu chọn cho đồ uống của cô ấy.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Đánh giá về người bạn đồng hành của bạn có thể thay đổi tùy thuộc vào nguyên liệu bạn chọn cho đồ uống của họ</t>
+          <t>Đánh giá của bạn đồng hành có thể thay đổi tùy vào nguyên liệu cậu chọn cho đồ uống của cô ấy.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Đánh giá về người bạn đồng hành của bạn có thể thay đổi tùy thuộc vào nguyên liệu bạn chọn cho đồ uống của họ</t>
+          <t>Đánh giá của bạn đồng hành có thể thay đổi tùy vào nguyên liệu cậu chọn cho đồ uống của cô ấy.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể chọn 2 vật phẩm bổ trợ</t>
+          <t>Cậu chỉ có thể chọn 2 phụ kiện thôi.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể chọn 2 vật phẩm bổ trợ</t>
+          <t>Cậu chỉ có thể chọn 2 phụ kiện thôi.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể chọn 2 vật phẩm bổ trợ</t>
+          <t>Cậu chỉ có thể chọn 2 phụ kiện thôi.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Invite đồng hành của bạn đến đây chơi bài</t>
+          <t>Mời đồng đội đến chơi bài tại đây</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>{0} mời bạn bè đến đây để chơi bài</t>
+          <t>Nhấn {0} để mời đồng đội cùng chơi bài tại đây</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Invite đồng hành của bạn đến đây chơi bài</t>
+          <t>Mời đồng đội đến chơi bài tại đây</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Switch đổi chế độ Chỉnh Sửa Data tại đây</t>
+          <t>Bật chế độ chỉnh sửa dữ liệu tại đây</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Switch đổi chế độ Chỉnh Sửa Data tại đây</t>
+          <t>Bật chế độ chỉnh sửa dữ liệu tại đây</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Switch đổi chế độ Chỉnh Sửa Data tại đây</t>
+          <t>Bật chế độ chỉnh sửa dữ liệu tại đây</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Switch đổi chế độ Chỉnh Sửa Data tại đây</t>
+          <t>Bật chế độ chỉnh sửa dữ liệu tại đây</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Switch đổi chế độ Chỉnh Sửa Data tại đây</t>
+          <t>Bật chế độ chỉnh sửa dữ liệu tại đây</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Switch đổi chế độ Chỉnh Sửa Data tại đây</t>
+          <t>Bật chế độ chỉnh sửa dữ liệu tại đây</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Đã mở khóa Hợp Nhất Chỉ Định. Bạn có thể chuyển đổi giữa hai chế độ</t>
+          <t>Hợp Nhất Có Mục Tiêu đã mở khóa. Bạn có thể chuyển đổi giữa hai chế độ</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Đã mở khóa Hợp Nhất Chỉ Định. Bạn có thể chuyển đổi giữa hai chế độ</t>
+          <t>Hợp Nhất Có Mục Tiêu đã mở khóa. Bạn có thể chuyển đổi giữa hai chế độ</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Đã mở khóa Hợp Nhất Chỉ Định. Bạn có thể chuyển đổi giữa hai chế độ</t>
+          <t>Hợp Nhất Có Mục Tiêu đã mở khóa. Bạn có thể chuyển đổi giữa hai chế độ</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem Mô-đun Mở Rộng của xe máy</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Mô-đun Mở Rộng của xe máy.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem Mô-đun Mở Rộng của xe máy</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Mô-đun Mở Rộng của xe máy.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để xem Mô-đun Mở Rộng của xe máy</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Mô-đun Mở Rộng của xe máy.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Tactic Mô-đun mới mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Mô-đun Chiến Thuật mới mở khóa.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Tactic Mô-đun mới mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Mô-đun Chiến Thuật mới mở khóa.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Tactic Mô-đun mới mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Mô-đun Chiến Thuật mới mở khóa.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển đổi để kích hoạt và sử dụng Mô-đun Chiến thuật mới</t>
+          <t>Ngươi có thể kích hoạt và sử dụng các Mô-đun Chiến Thuật mới</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển đổi để kích hoạt và sử dụng Mô-đun Chiến thuật mới</t>
+          <t>Ngươi có thể kích hoạt và sử dụng các Mô-đun Chiến Thuật mới</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Bạn có thể chuyển đổi để kích hoạt và sử dụng Mô-đun Chiến thuật mới</t>
+          <t>Ngươi có thể kích hoạt và sử dụng các Mô-đun Chiến Thuật mới</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Echoes Managementes đã bật. Echoes nhận được sẽ tự động phân loại theo loại.</t>
+          <t>Đã Bật Quản Lý Tiếng Vọng. Các Tiếng Vọng Nhận Được Sẽ Tự Động Phân Loại Theo Chủng Loại.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Echoes Managementes đã bật. Echoes nhận được sẽ tự động phân loại theo loại.</t>
+          <t>Đã Bật Quản Lý Tiếng Vọng. Các Tiếng Vọng Nhận Được Sẽ Tự Động Phân Loại Theo Chủng Loại.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Echoes Managementes đã bật. Echoes nhận được sẽ tự động phân loại theo loại.</t>
+          <t>Đã Bật Quản Lý Tiếng Vọng. Các Tiếng Vọng Nhận Được Sẽ Tự Động Phân Loại Theo Chủng Loại.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Khởi động Quản lý tự động tại đây.</t>
+          <t>Bắt đầu Quản lý Tự động tại đây.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Khởi động Quản lý tự động tại đây.</t>
+          <t>Bắt đầu Quản lý Tự động tại đây.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Khởi động Quản lý tự động tại đây.</t>
+          <t>Bắt đầu Quản lý Tự động tại đây.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để chỉnh Quản lý Auto.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để chỉnh sửa Tự Động Quản Lý.</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để chỉnh Quản lý Auto.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để chỉnh sửa Tự Động Quản Lý.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để chỉnh Quản lý Auto.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để chỉnh sửa Tự Động Quản Lý.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Invite đồng hành khác đến đây sau khi hoàn thành trò chơi trước</t>
+          <t>Mời bạn bè khác đến đây sau khi hoàn thành trò chơi trước</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Invite đồng hành khác đến đây sau khi hoàn thành trò chơi trước</t>
+          <t>Mời bạn bè khác đến đây sau khi hoàn thành trò chơi trước</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Invite đồng hành khác đến đây sau khi hoàn thành trò chơi trước</t>
+          <t>Mời bạn bè khác đến đây sau khi hoàn thành trò chơi trước</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Boost đã hồi phục đầy đủ; thả kỹ năng để tăng tốc ngay lập tức</t>
+          <t>Tăng cường đã hồi phục hoàn toàn; thả kỹ năng để tăng tốc ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Tăng tốc đã hồi đầy; {Cus:Ipt,Touch=Touch PC=click Gamepad=press} {0} để giải phóng kỹ năng và tăng tốc ngay lập tức</t>
+          <t>Năng lượng Boost đã hồi đầy; {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} {0} để giải phóng kỹ năng và tăng tốc ngay lập tức</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Boost đã hồi phục đầy đủ; thả kỹ năng để tăng tốc ngay lập tức</t>
+          <t>Tăng cường đã hồi phục hoàn toàn; thả kỹ năng để tăng tốc ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tham gia các hoạt động Fest khác nhau từ đây</t>
+          <t>Tham gia các hoạt động lễ hội khác nhau từ đây</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tham gia các hoạt động Fest khác nhau từ đây</t>
+          <t>Tham gia các hoạt động lễ hội khác nhau từ đây</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Tham gia các hoạt động Fest khác nhau từ đây</t>
+          <t>Tham gia các hoạt động lễ hội khác nhau từ đây</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Switch đổi vũ khí hiển thị tại đây</t>
+          <t>Đổi vũ khí hiển thị tại đây</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Switch đổi vũ khí hiển thị tại đây</t>
+          <t>Đổi vũ khí hiển thị tại đây</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Dùng Heavy Attack để tối đa hóa Tỷ lệ Đồng bộ</t>
+          <t>Thực hiện Đòn Heavy Attack để tối đa hóa Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Dùng Heavy Attack để tối đa hóa Tỷ lệ Đồng bộ</t>
+          <t>Thực hiện Đòn Heavy Attack để tối đa hóa Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Dùng Heavy Attack để tối đa hóa Tỷ lệ Đồng bộ</t>
+          <t>Thực hiện Đòn Heavy Attack để tối đa hóa Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Switch đổi vũ khí hiển thị tại đây</t>
+          <t>Đổi vũ khí hiển thị tại đây</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để bắt đầu Tutorial Track</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu Hướng dẫn Theo dõi</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để bắt đầu Tutorial Track</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu Hướng dẫn Theo dõi</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để bắt đầu Tutorial Track</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu Hướng dẫn Theo dõi</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu thử thách</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu thử thách</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để bắt đầu thử thách</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} khi Nốt Xanh xuất hiện trên Bài Nhạc</t>
+          <t>Nhấn {0} khi Nốt Nhạc Lục xuất hiện trên Đường Đua</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} khi Nốt Xanh xuất hiện trên Bài Nhạc</t>
+          <t>Nhấn {0} khi Nốt Nhạc Lục xuất hiện trên Đường Đua</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} Button Xanh khi Xuất Hiện Nốt Xanh trên Đường Nhạc</t>
+          <t>Nhấn nút Lục khi Nốt Lục xuất hiện trên Đường Nhạc.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} khi Nốt Xanh xuất hiện trên Bài Nhạc</t>
+          <t>Nhấn {0} khi Nốt Nhạc Xanh xuất hiện trên Đường Đua</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} khi Nốt Xanh xuất hiện trên Bài Nhạc</t>
+          <t>Nhấn {0} khi Nốt Nhạc Xanh xuất hiện trên Đường Đua</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} nút Xanh khi nốt Xanh xuất hiện trên Đường Nhạc</t>
+          <t>Nhấn nút Xanh khi Nốt Xanh xuất hiện trên Đường Nhạc.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Bây giờ {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Right để điều khiển tàu vũ trụ sang phải</t>
+          <t>Bây giờ {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Phải để điều khiển tàu vũ trụ sang phải</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút {0} để đánh trúng Ghi chú đúng lúc</t>
+          <t>Nhấn nút {0} để đánh Nốt đúng nhịp.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút {0} để đánh trúng Ghi chú đúng lúc</t>
+          <t>Nhấn nút {0} để đánh Nốt đúng nhịp.</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Vàng để đánh trúng Nốt đúng lúc</t>
+          <t>Nhấn nút Vàng để đánh Nốt đúng nhịp.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Giữ nút Vàng</t>
+          <t>Giữ Nút Vàng</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đánh trúng nốt nhạc đúng lúc sẽ tăng hệ số tính điểm và tốc độ bay</t>
+          <t>Đánh trúng nốt nhạc đúng lúc sẽ tăng hệ số nhân điểm và tốc độ bay.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đánh trúng nốt nhạc đúng lúc sẽ tăng hệ số tính điểm và tốc độ bay</t>
+          <t>Đánh trúng nốt nhạc đúng lúc sẽ tăng hệ số nhân điểm và tốc độ bay.</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Đánh trúng nốt nhạc đúng lúc sẽ tăng hệ số tính điểm và tốc độ bay</t>
+          <t>Đánh trúng nốt nhạc đúng lúc sẽ tăng hệ số nhân điểm và tốc độ bay.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Đạt xếp hạng cao hơn A ở độ khó Dễ để mở khóa thêm các mức độ khó khác</t>
+          <t>Đạt xếp hạng trên A ở độ khó Dễ để mở khóa các độ khó cao hơn</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Đạt xếp hạng cao hơn A ở độ khó Dễ để mở khóa thêm các mức độ khó khác</t>
+          <t>Đạt xếp hạng trên A ở độ khó Dễ để mở khóa các độ khó cao hơn</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Đạt xếp hạng cao hơn A ở độ khó Dễ để mở khóa thêm các mức độ khó khác</t>
+          <t>Đạt xếp hạng trên A ở độ khó Dễ để mở khóa các độ khó cao hơn</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Tiếp tục thử thách ở độ khó Thường</t>
+          <t>Tiếp tục thử thách ở độ khó Bình thường</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Tiếp tục thử thách ở độ khó Thường</t>
+          <t>Tiếp tục thử thách ở độ khó Bình thường</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tiếp tục thử thách ở độ khó Thường</t>
+          <t>Tiếp tục thử thách ở độ khó Bình thường</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tiếp tục bay để tích năng lượng và vào Full Speed Mode, cho phép tự động đánh trúng các Ghi chú</t>
+          <t>Tiếp tục bay để tích năng lượng và kích hoạt Chế Độ Tốc Độ Tối Đa, cho phép tự động đánh trúng các Nốt Nhạc</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tiếp tục bay để tích năng lượng và vào Full Speed Mode, cho phép tự động đánh trúng các Ghi chú</t>
+          <t>Tiếp tục bay để tích năng lượng và kích hoạt Chế Độ Tốc Độ Tối Đa, cho phép tự động đánh trúng các Nốt Nhạc</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tiếp tục bay để tích năng lượng và vào Full Speed Mode, cho phép tự động đánh trúng các Ghi chú</t>
+          <t>Tiếp tục bay để tích năng lượng và kích hoạt Chế Độ Tốc Độ Tối Đa, cho phép tự động đánh trúng các Nốt Nhạc</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Resonators đã mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Resonator đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} {0} để xem Resonators đã mở khóa</t>
+          <t>Nhấn {0} để xem Resonator đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Resonators đã mở khóa</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem các Resonator đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Mỗi Resonator đồng hành sẽ cấp một hiệu ứng tăng cường độc đáo</t>
+          <t>Mỗi Resonator đồng hành sẽ mang đến một hiệu ứng tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mỗi Resonator đồng hành sẽ cấp một hiệu ứng tăng cường độc đáo</t>
+          <t>Mỗi Resonator đồng hành sẽ mang đến một hiệu ứng tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Mỗi Resonator đồng hành sẽ cấp một hiệu ứng tăng cường độc đáo</t>
+          <t>Mỗi Resonator đồng hành sẽ mang đến một hiệu ứng tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Resonator được chọn sẽ là bạn đồng hành của bạn trong giai đoạn này</t>
+          <t>Resonator cậu chọn sẽ đồng hành cùng cậu trong giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Resonator được chọn sẽ là bạn đồng hành của bạn trong giai đoạn này</t>
+          <t>Resonator cậu chọn sẽ đồng hành cùng cậu trong giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Resonator được chọn sẽ là bạn đồng hành của bạn trong giai đoạn này</t>
+          <t>Resonator cậu chọn sẽ đồng hành cùng cậu trong giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm điểm Gourmet</t>
+          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm Điểm Ẩm Thực</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm điểm Gourmet</t>
+          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm Điểm Ẩm Thực</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm điểm Gourmet</t>
+          <t>Di chuyển Resonator sang trái hoặc phải để thu thập thức ăn và kiếm Điểm Ẩm Thực</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Thu thập thức ăn cũng giúp phục hồi Năng Lượng.</t>
+          <t>Thu thập thức ăn cũng giúp hồi phục Năng lượng</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Thu thập thức ăn cũng giúp phục hồi Năng Lượng.</t>
+          <t>Thu thập thức ăn cũng giúp hồi phục Năng lượng</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Thu thập thức ăn cũng giúp phục hồi Năng Lượng.</t>
+          <t>Thu thập thức ăn cũng giúp hồi phục Năng lượng</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng đầy, Resonator Skill sẽ sẵn sàng sử dụng</t>
+          <t>Khi Năng Lượng đầy, Kỹ Năng Cộng Hưởng sẽ sẵn sàng</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để sử dụng Resonator Skill</t>
+          <t>Khi Năng Lượng đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để sử dụng Kỹ Năng Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng đầy, Resonator Skill sẽ sẵn sàng sử dụng</t>
+          <t>Khi Năng Lượng đầy, Kỹ Năng Cộng Hưởng sẽ sẵn sàng</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Xem tác dụng của thức ăn sưu tầm cho thử thách hiện tại tại đây</t>
+          <t>Xem tác dụng của thức ăn sưu tầm cho thử thách hiện tại tại đây.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>{0} View tác dụng của thức ăn sưu tầm cho thử thách hiện tại tại đây</t>
+          <t>Xem tác dụng của thức ăn thu thập được cho thử thách hiện tại tại đây</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Xem tác dụng của thức ăn sưu tầm cho thử thách hiện tại tại đây</t>
+          <t>Xem tác dụng của thức ăn sưu tầm cho thử thách hiện tại tại đây.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Năng lượng đã nạp đầy! Đến lúc dùng Skill rồi!</t>
+          <t>Năng lượng đã nạp đầy! Đến lúc sử dụng Kỹ Năng rồi!</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Năng lượng đã nạp đầy! Nhấn {0} để sử dụng Kỹ Năng ngay!</t>
+          <t>Năng lượng đã nạp đầy! {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} để sử dụng Kỹ Năng ngay!</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Năng lượng đã nạp đầy! Đến lúc dùng Skill rồi!</t>
+          <t>Năng lượng đã nạp đầy! Đến lúc sử dụng Kỹ Năng rồi!</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Mỗi ngày có một Resonator mới xuất hiện</t>
+          <t>Mỗi ngày lại có một Resonator mới đến</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>{0} View Resonator mới của ngày hôm nay</t>
+          <t>Xem Resonator mới của ngày hôm nay</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Mỗi ngày có một Resonator mới xuất hiện</t>
+          <t>Mỗi ngày lại có một Resonator mới đến</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Kéo các khối từ bên phải vào khoảng trống ở giữa</t>
+          <t>Kéo các khối từ bên phải vào để lấp đầy khoảng trống ở giữa</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Kéo các khối từ bên phải vào khoảng trống ở giữa</t>
+          <t>Kéo các khối từ bên phải vào để lấp đầy khoảng trống ở giữa</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Kéo các khối từ bên phải vào khoảng trống ở giữa</t>
+          <t>Kéo các khối từ bên phải vào để lấp đầy khoảng trống ở giữa</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành một hàng hoặc cột đầy để xóa các khối</t>
+          <t>Hoàn thành một hàng hoặc cột để xóa các khối</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn thành một hàng hoặc cột đầy để xóa các khối</t>
+          <t>Hoàn thành một hàng hoặc cột để xóa các khối</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hoàn thành một hàng hoặc cột đầy để xóa các khối</t>
+          <t>Hoàn thành một hàng hoặc cột để xóa các khối</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Clear các khối để kiếm điểm và đạt điểm mục tiêu để qua màn</t>
+          <t>Phá hủy các khối để kiếm điểm và đạt điểm mục tiêu để hoàn thành màn chơi</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Clear các khối để kiếm điểm và đạt điểm mục tiêu để qua màn</t>
+          <t>Phá hủy các khối để kiếm điểm và đạt điểm mục tiêu để hoàn thành màn chơi</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Clear các khối để kiếm điểm và đạt điểm mục tiêu để qua màn</t>
+          <t>Phá hủy các khối để kiếm điểm và đạt điểm mục tiêu để hoàn thành màn chơi</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Clear các khối chứa Huy Chương để thu thập chúng</t>
+          <t>Phá hủy các khối chứa Huy Chương để thu thập chúng</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Clear các khối chứa Huy Chương để thu thập chúng</t>
+          <t>Phá hủy các khối chứa Huy Chương để thu thập chúng</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Clear các khối chứa Huy Chương để thu thập chúng</t>
+          <t>Phá hủy các khối chứa Huy Chương để thu thập chúng</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Huy Chương để hoàn thành giai đoạn.</t>
+          <t>Thu thập đủ số Huy Chương yêu cầu để hoàn thành màn chơi.</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Huy Chương để hoàn thành giai đoạn.</t>
+          <t>Thu thập đủ số Huy Chương yêu cầu để hoàn thành màn chơi.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng Huy Chương để hoàn thành giai đoạn.</t>
+          <t>Thu thập đủ số Huy Chương yêu cầu để hoàn thành màn chơi.</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Clear khối để kiếm điểm</t>
+          <t>Phá hủy các khối để kiếm điểm</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Clear khối để kiếm điểm</t>
+          <t>Phá hủy các khối để kiếm điểm</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Clear khối để kiếm điểm</t>
+          <t>Phá hủy các khối để kiếm điểm</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem thử thách Stability Accords</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thử thách Stability Accords.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem thử thách Stability Accords</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thử thách Stability Accords.</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem thử thách Stability Accords</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xem thử thách Stability Accords.</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự như đã liệt kê.</t>
+          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự đã sắp xếp.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự như đã liệt kê.</t>
+          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự đã sắp xếp.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự như đã liệt kê.</t>
+          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự đã sắp xếp.</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Trong thử thách Stability Accords, bạn có thể triển khai tối đa ba đội</t>
+          <t>Trong thử thách Hiệp Ước Ổn Định, bạn có thể triển khai tối đa ba đội.</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Trong thử thách Stability Accords, bạn có thể triển khai tối đa ba đội</t>
+          <t>Trong thử thách Hiệp Ước Ổn Định, bạn có thể triển khai tối đa ba đội.</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Trong thử thách Stability Accords, bạn có thể triển khai tối đa ba đội</t>
+          <t>Trong thử thách Hiệp Ước Ổn Định, bạn có thể triển khai tối đa ba đội.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Sau khi chọn đội hình, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để chuẩn bị cho thử thách</t>
+          <t>Sau khi chọn đội hình, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để chuẩn bị cho thử thách.</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Sau khi chọn đội hình, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để chuẩn bị cho thử thách</t>
+          <t>Sau khi chọn đội hình, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để chuẩn bị cho thử thách.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Sau khi chọn đội hình, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để chuẩn bị cho thử thách</t>
+          <t>Sau khi chọn đội hình, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để chuẩn bị cho thử thách.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Mỗi kẻ địch có một khả năng đặc biệt gọi là Escalation</t>
+          <t>Mỗi kẻ địch đều sở hữu một kỹ năng đặc biệt gọi là Escalation.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Mỗi kẻ địch có một khả năng đặc biệt gọi là Escalation</t>
+          <t>Mỗi kẻ địch đều sở hữu một kỹ năng đặc biệt gọi là Escalation.</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Mỗi kẻ địch có một khả năng đặc biệt gọi là Escalation</t>
+          <t>Mỗi kẻ địch đều sở hữu một kỹ năng đặc biệt gọi là Escalation.</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Chọn Power Circuit tại đây để nhận buff cho đội hiện tại.</t>
+          <t>Chọn Mạch Năng Lượng tại đây để nhận hiệu ứng tăng cường cho đội hiện tại.</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Chọn Power Circuit tại đây để nhận buff cho đội hiện tại.</t>
+          <t>Chọn Mạch Năng Lượng tại đây để nhận hiệu ứng tăng cường cho đội hiện tại.</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Chọn Power Circuit tại đây để nhận buff cho đội hiện tại.</t>
+          <t>Chọn Mạch Năng Lượng tại đây để nhận hiệu ứng tăng cường cho đội hiện tại.</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Chọn Demo Resonators tại đây, sẽ khả dụng sau khi mở khóa Resonators tương ứng</t>
+          <t>Chọn Resonator Demo tại đây, chúng sẽ xuất hiện sau khi mở khóa Resonator tương ứng</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Chọn Demo Resonators tại đây, sẽ khả dụng sau khi mở khóa Resonators tương ứng</t>
+          <t>Chọn Resonator Demo tại đây, chúng sẽ xuất hiện sau khi mở khóa Resonator tương ứng</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Chọn Demo Resonators tại đây, sẽ khả dụng sau khi mở khóa Resonators tương ứng</t>
+          <t>Chọn Resonator Demo tại đây, chúng sẽ xuất hiện sau khi mở khóa Resonator tương ứng</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Xem nhiệm vụ và phần thưởng khả dụng cho Chu Kỳ Thử Thách hiện tại tại đây.</t>
+          <t>Xem nhiệm vụ và phần thưởng của Chu kỳ Thử Thách hiện tại tại đây</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Xem nhiệm vụ và phần thưởng khả dụng cho Chu Kỳ Thử Thách hiện tại tại đây.</t>
+          <t>Xem nhiệm vụ và phần thưởng của Chu kỳ Thử Thách hiện tại tại đây</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>{0} Bộ lọc Echo đã được nâng cấp</t>
+          <t>Bộ lọc Echo đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>{0} Bộ lọc Echo đã được nâng cấp</t>
+          <t>Bộ lọc Echo đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>{0} Bộ lọc Echo đã được nâng cấp</t>
+          <t>Bộ lọc Echo đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>{0} Bộ lọc Echo đã được nâng cấp</t>
+          <t>Bộ lọc Echo đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>{0} Bộ lọc Echo đã được nâng cấp</t>
+          <t>Bộ lọc Echo đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Filter Echo đã được nâng cấp</t>
+          <t>Bộ lọc Cộng Hưởng đã được nâng cấp</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Quản lý lô Echo giờ đã được nâng cấp với chức năng Loại bỏ thông minh</t>
+          <t>Quản Lý Lô Echo nay đã được nâng cấp với tính năng Loại Bỏ Thông Minh</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>{0} Quản Lý Echo Hàng Loạt hiện đã được nâng cấp với chức năng Smart Discard</t>
+          <t>Quản lý lô Echo đã được nâng cấp với chức năng Loại Bỏ Thông Minh</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Quản lý lô Echo giờ đã được nâng cấp với chức năng Loại bỏ thông minh</t>
+          <t>Quản Lý Lô Echo nay đã được nâng cấp với tính năng Loại Bỏ Thông Minh</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Bạn có thể nhanh chóng loại bỏ Echoes dư thừa bằng Smart Discard</t>
+          <t>Giờ cậu có thể nhanh chóng loại bỏ Echo dư thừa bằng Tính Năng Loại Bỏ Thông Minh.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>{0} Bạn giờ đây có thể loại bỏ nhanh Echoes dư thừa bằng Smart Discard</t>
+          <t>{0} Giờ cậu có thể nhanh chóng loại bỏ Echo dư thừa bằng Smart Discard</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Bạn có thể nhanh chóng loại bỏ Echoes dư thừa bằng Smart Discard</t>
+          <t>Giờ cậu có thể nhanh chóng loại bỏ Echo dư thừa bằng Tính Năng Loại Bỏ Thông Minh.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Truy cập Những Whispers Between Stars qua Guide Khu Vực</t>
+          <t>Đến Vùng Giao Thoa Giữa Các Vì Sao qua Hướng Dẫn Khu Vực</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>{0} Truy cập Whispers Between Stars qua Hướng dẫn Khu vực</t>
+          <t>{0} Truy cập Lời Thì Thầm Giữa Các Vì Sao qua Hướng Dẫn Khu Vực</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Truy cập Những Whispers Between Stars qua Guide Khu Vực</t>
+          <t>Đến Vùng Giao Thoa Giữa Các Vì Sao qua Hướng Dẫn Khu Vực</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Thì Thầm Sao Đêm của Lynae và Mornye đã được mở khóa</t>
+          <t>Đã mở khóa "Lời thì thầm sao" của Lynae và Mornye</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Thì Thầm Sao Đêm của Lynae và Mornye đã được mở khóa</t>
+          <t>Đã mở khóa "Lời thì thầm sao" của Lynae và Mornye</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Thì Thầm Sao Đêm của Lynae và Mornye đã được mở khóa</t>
+          <t>Đã mở khóa "Lời thì thầm sao" của Lynae và Mornye</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Đã mở khóa Luuk Herssen và Lời Thì Thầm Ngôi Sao của Lucilla</t>
+          <t>Luuk Herssen và Lời Thì Thầm Sao của Lucilla đã được mở khóa</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Đã mở khóa Luuk Herssen và Lời Thì Thầm Ngôi Sao của Lucilla</t>
+          <t>Luuk Herssen và Lời Thì Thầm Sao của Lucilla đã được mở khóa</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Đã mở khóa Luuk Herssen và Lời Thì Thầm Ngôi Sao của Lucilla</t>
+          <t>Luuk Herssen và Lời Thì Thầm Sao của Lucilla đã được mở khóa</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Xem nhiệm vụ và phần thưởng khả dụng cho Chu Kỳ Thử Thách hiện tại tại đây.</t>
+          <t>Xem nhiệm vụ và phần thưởng của Chu kỳ Thử Thách hiện tại tại đây</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để mở trang Knights of the Wild</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở trang Knights of the Wild</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để mở trang Knights of the Wild</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở trang Knights of the Wild</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để mở trang Knights of the Wild</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để mở trang Knights of the Wild</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để bắt đầu Exam</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để bắt đầu bài kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để bắt đầu Exam</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để bắt đầu bài kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để bắt đầu Exam</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để bắt đầu bài kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Explore và chiến đấu để tăng Cấp Độ GPA và kích hoạt buff.</t>
+          <t>Khám phá và chiến đấu để tăng Cấp Độ GPA và kích hoạt hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Explore và chiến đấu để tăng Cấp Độ GPA và kích hoạt buff.</t>
+          <t>Khám phá và chiến đấu để tăng Cấp Độ GPA và kích hoạt hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Explore và chiến đấu để tăng Cấp Độ GPA và kích hoạt buff.</t>
+          <t>Khám phá và chiến đấu để tăng Cấp Độ GPA và kích hoạt hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout.</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout.</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Thực hiện hành động trong Kỳ Thi có thể tăng GPA Level Tạm Thời và cung cấp buff chiến đấu</t>
+          <t>Hành động trong Kỳ Thi có thể nâng Cấp Điểm GPA Tạm Thời và mang lại hiệu ứng hỗ trợ chiến đấu</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Thực hiện hành động trong Kỳ Thi có thể tăng GPA Level Tạm Thời và cung cấp buff chiến đấu</t>
+          <t>Hành động trong Kỳ Thi có thể nâng Cấp Điểm GPA Tạm Thời và mang lại hiệu ứng hỗ trợ chiến đấu</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Thực hiện hành động trong Kỳ Thi có thể tăng GPA Level Tạm Thời và cung cấp buff chiến đấu</t>
+          <t>Hành động trong Kỳ Thi có thể nâng Cấp Điểm GPA Tạm Thời và mang lại hiệu ứng hỗ trợ chiến đấu</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Buff Overview để xem các buff đã kích hoạt</t>
+          <t>Nhấn Buff Overview để xem các hiệu ứng đã kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Buff Overview để xem các buff đã kích hoạt</t>
+          <t>Nhấn Buff Overview để xem các hiệu ứng đã kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} Buff Overview để xem các buff đã kích hoạt</t>
+          <t>Nhấn Buff Overview để xem các hiệu ứng đã kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Nâng cấp GPA để kích hoạt buff</t>
+          <t>Tăng Cấp GPA để kích hoạt hiệu ứng hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Nâng cấp GPA để kích hoạt buff</t>
+          <t>Tăng Cấp GPA để kích hoạt hiệu ứng hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nâng cấp GPA để kích hoạt buff</t>
+          <t>Tăng Cấp GPA để kích hoạt hiệu ứng hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấn chuột Gamepad=Nhấn} để chọn Đại Hiệp Sĩ</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn Grand Knight.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấn chuột Gamepad=Nhấn} để chọn Đại Hiệp Sĩ</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn Grand Knight.</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấn chuột Gamepad=Nhấn} để chọn Đại Hiệp Sĩ</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn Grand Knight.</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi.</t>
+          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi.</t>
+          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi.</t>
+          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Xem cơ chế đặc biệt của Examiner tại đây</t>
+          <t>Xem cơ chế đặc biệt của Giám Khảo tại đây</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Xem cơ chế đặc biệt của Examiner tại đây</t>
+          <t>Xem cơ chế đặc biệt của Giám Khảo tại đây</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Xem cơ chế đặc biệt của Examiner tại đây</t>
+          <t>Xem cơ chế đặc biệt của Giám Khảo tại đây</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>GPA Level nhận được từ việc sửa chữa các Hiệp sĩ sẽ có hiệu lực vĩnh viễn.</t>
+          <t>Cấp GPA nhận được từ việc sửa chữa các Hiệp Sĩ sẽ có hiệu lực vĩnh viễn.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>GPA Level nhận được từ việc sửa chữa các Hiệp sĩ sẽ có hiệu lực vĩnh viễn.</t>
+          <t>Cấp GPA nhận được từ việc sửa chữa các Hiệp Sĩ sẽ có hiệu lực vĩnh viễn.</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>GPA Level nhận được từ việc sửa chữa các Hiệp sĩ sẽ có hiệu lực vĩnh viễn.</t>
+          <t>Cấp GPA nhận được từ việc sửa chữa các Hiệp Sĩ sẽ có hiệu lực vĩnh viễn.</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấp chuột Gamepad=Nhấn} để xem vị trí của các Hiệp Sĩ và thông tin Examiner</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem vị trí của các Hiệp Sĩ và thông tin về Giám Khảo.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấp chuột Gamepad=Nhấn} để xem vị trí của các Hiệp Sĩ và thông tin Examiner</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem vị trí của các Hiệp Sĩ và thông tin về Giám Khảo.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấp chuột Gamepad=Nhấn} để xem vị trí của các Hiệp Sĩ và thông tin Examiner</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem vị trí của các Hiệp Sĩ và thông tin về Giám Khảo.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Bạn có thể thiết lập hệ thống để tự động khóa hoặc loại bỏ các Echoes mới nhận được</t>
+          <t>Bạn có thể thiết lập hệ thống tự động khóa hoặc loại bỏ Echo mới nhận được</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Bạn có thể thiết lập hệ thống để tự động khóa hoặc loại bỏ các Echoes mới nhận được</t>
+          <t>Bạn có thể thiết lập hệ thống tự động khóa hoặc loại bỏ Echo mới nhận được</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Bạn có thể thiết lập hệ thống để tự động khóa hoặc loại bỏ các Echoes mới nhận được</t>
+          <t>Bạn có thể thiết lập hệ thống tự động khóa hoặc loại bỏ Echo mới nhận được</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Khi bật, tất cả Echoes không phải 5 sao sẽ tự động được đánh dấu là "Loại bỏ"</t>
+          <t>Khi bật, tất cả Cộng Hưởng không phải 5 sao sẽ tự động đánh dấu là "Loại bỏ".</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Khi bật, tất cả Echoes không phải 5 sao sẽ tự động được đánh dấu là "Loại bỏ"</t>
+          <t>Khi bật, tất cả Cộng Hưởng không phải 5 sao sẽ tự động đánh dấu là "Loại bỏ".</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Khi bật, tất cả Echoes không phải 5 sao sẽ tự động được đánh dấu là "Loại bỏ"</t>
+          <t>Khi bật, tất cả Cộng Hưởng không phải 5 sao sẽ tự động đánh dấu là "Loại bỏ".</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Bạn có thể đặt tất cả kế hoạch về cấu hình đề xuất</t>
+          <t>Bạn có thể thiết lập tất cả kế hoạch theo các gợi ý đề xuất</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Bạn có thể đặt tất cả kế hoạch về cấu hình đề xuất</t>
+          <t>Bạn có thể thiết lập tất cả kế hoạch theo các gợi ý đề xuất</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Bạn có thể đặt tất cả kế hoạch về cấu hình đề xuất</t>
+          <t>Bạn có thể thiết lập tất cả kế hoạch theo các gợi ý đề xuất</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>{0} Dùng Rune: Nhấn Switch để thay đổi trạng thái Switchgate trong môi trường này</t>
+          <t>Dùng Rune: Switch để thay đổi trạng thái của Switchgate trong môi trường này.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Dùng Rune: Switch để thay đổi trạng thái Switchgate trong môi trường này</t>
+          <t>Dùng Rune: Switch để thay đổi trạng thái của Switchgate trong môi trường này.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Enter trang hiệu chỉnh tại đây</t>
+          <t>Truy cập trang hiệu chuẩn tại đây</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Enter trang hiệu chỉnh tại đây</t>
+          <t>Truy cập trang hiệu chuẩn tại đây</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Enter trang hiệu chỉnh tại đây</t>
+          <t>Truy cập trang hiệu chuẩn tại đây</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấp chuột Gamepad=Nhấn} vào đây để vào giao diện hiệu chuẩn</t>
+          <t>Nhấn vào đây để vào giao diện hiệu chuẩn.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấp chuột Gamepad=Nhấn} vào đây để vào giao diện hiệu chuẩn</t>
+          <t>Nhấn vào đây để vào giao diện hiệu chuẩn.</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm PC=Nhấp chuột Gamepad=Nhấn} vào đây để vào giao diện hiệu chuẩn</t>
+          <t>Nhấn vào đây để vào giao diện hiệu chuẩn.</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Điều chỉnh giá trị offset về trạng thái phù hợp với bạn</t>
+          <t>Hiệu chỉnh giá trị lệch pha cho phù hợp với cậu</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Điều chỉnh giá trị offset về trạng thái phù hợp với bạn</t>
+          <t>Hiệu chỉnh giá trị lệch pha cho phù hợp với cậu</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Điều chỉnh giá trị offset về trạng thái phù hợp với bạn</t>
+          <t>Hiệu chỉnh giá trị lệch pha cho phù hợp với cậu</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để bắt đầu hiệu chỉnh</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để bắt đầu hiệu chỉnh.</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút {0} để bắt đầu hiệu chỉnh</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút {0} để bắt đầu hiệu chỉnh.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để bắt đầu hiệu chỉnh</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để bắt đầu hiệu chỉnh.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>{0} View chi tiết Bài thi và tiến độ sửa chữa Mechascout tại đây</t>
+          <t>Xem chi tiết Kỳ Thi và tiến độ sửa chữa Mechascout tại đây</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào Overview Buff để xem các buff đã kích hoạt</t>
+          <t>{0} {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào "Tổng Quan Buff" để xem các hiệu ứng đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>{0} View thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Details Kỳ Thi</t>
+          <t>Xem thông tin Giám Khảo và tiến độ sửa chữa Hiệp Sĩ trong Chi Tiết Kỳ Thi</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Tại đây, bạn có thể bật/tắt Live Chat, chọn biểu cảm và gửi tin nhắn.</t>
+          <t>Tại đây, cậu có thể bật/tắt Trò Chuyện Trực Tiếp, chọn biểu cảm và gửi tin nhắn.</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tại đây, bạn có thể bật/tắt Live Chat, chọn biểu cảm và gửi tin nhắn.</t>
+          <t>Tại đây, cậu có thể bật/tắt Trò Chuyện Trực Tiếp, chọn biểu cảm và gửi tin nhắn.</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Tại đây, bạn có thể bật/tắt Live Chat, chọn biểu cảm và gửi tin nhắn.</t>
+          <t>Tại đây, cậu có thể bật/tắt Trò Chuyện Trực Tiếp, chọn biểu cảm và gửi tin nhắn.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Tại đây bạn có thể xem chi tiết về các cơ chế đường đua sẽ xuất hiện.</t>
+          <t>Tại đây, cậu có thể xem chi tiết về cơ chế đường ray sẽ xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Tại đây bạn có thể xem chi tiết về các cơ chế đường đua sẽ xuất hiện.</t>
+          <t>Tại đây, cậu có thể xem chi tiết về cơ chế đường ray sẽ xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Tại đây bạn có thể xem chi tiết về các cơ chế đường đua sẽ xuất hiện.</t>
+          <t>Tại đây, cậu có thể xem chi tiết về cơ chế đường ray sẽ xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn yêu cầu tập trung vào những điều khác nhau.</t>
+          <t>Màn hình này hiển thị giai đoạn hiện tại của cuộc đua. Mỗi giai đoạn sẽ yêu cầu tập trung vào những mục tiêu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Đây là những Cube đang chuẩn bị cho trận đấu tiếp theo.</t>
+          <t>Đây là những Cube chuẩn bị cho trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Đây là những Cube đang chuẩn bị cho trận đấu tiếp theo.</t>
+          <t>Đây là những Cube chuẩn bị cho trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Đây là những Cube đang chuẩn bị cho trận đấu tiếp theo.</t>
+          <t>Đây là những Cube chuẩn bị cho trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Hiển thị thời gian bắt đầu của trận đấu tiếp theo.</t>
+          <t>Màn hình này hiển thị thời gian bắt đầu trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Hiển thị thời gian bắt đầu của trận đấu tiếp theo.</t>
+          <t>Màn hình này hiển thị thời gian bắt đầu trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Hiển thị thời gian bắt đầu của trận đấu tiếp theo.</t>
+          <t>Màn hình này hiển thị thời gian bắt đầu trận đấu tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ hàng ngày để nhận Điểm Phổ Biến.</t>
+          <t>Hoàn thành nhiệm vụ hàng ngày sẽ giúp bạn nhận được Độ Nổi Tiếng.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ hàng ngày sẽ giúp bạn nhận được Độ Nổi Tiếng {0}.</t>
+          <t>Hoàn thành nhiệm vụ hằng ngày sẽ giúp cậu kiếm được Độ Phổ Biến.</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ hàng ngày để nhận Điểm Phổ Biến.</t>
+          <t>Hoàn thành nhiệm vụ hàng ngày sẽ giúp bạn nhận được Độ Nổi Tiếng.</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Chọn một Cube để Hỗ Trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó thắng.</t>
+          <t>Chọn một Khối Lập Phương để hỗ trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó chiến thắng</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chọn một Cube để Hỗ Trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó thắng.</t>
+          <t>Chọn một Khối Lập Phương để hỗ trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó chiến thắng</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Chọn một Cube để Hỗ Trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó thắng.</t>
+          <t>Chọn một Khối Lập Phương để hỗ trợ và nhận lượng lớn Độ Nổi Tiếng nếu nó chiến thắng</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Khối Cube có Tỷ Lệ Thua Cao hơn sẽ mang lại nhiều phần thưởng Popularity hơn nếu chiến thắng.</t>
+          <t>Khối Lập Phương có Tỷ Lệ Thua Lợi Nhuận cao hơn sẽ mang lại phần thưởng Danh Vọng nhiều hơn nếu chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Khối Cube có Tỷ Lệ Thua Cao hơn sẽ mang lại nhiều phần thưởng Popularity hơn nếu chiến thắng.</t>
+          <t>Khối Lập Phương có Tỷ Lệ Thua Lợi Nhuận cao hơn sẽ mang lại phần thưởng Danh Vọng nhiều hơn nếu chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Khối Cube có Tỷ Lệ Thua Cao hơn sẽ mang lại nhiều phần thưởng Popularity hơn nếu chiến thắng.</t>
+          <t>Khối Lập Phương có Tỷ Lệ Thua Lợi Nhuận cao hơn sẽ mang lại phần thưởng Danh Vọng nhiều hơn nếu chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tiêu hao lượng Popularity khác nhau để hỗ trợ Cube hiện tại của bạn</t>
+          <t>Tiêu thụ Lượng Yêu Thích để hỗ trợ Khối Lập Phương hiện tại.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Tiêu hao lượng Popularity khác nhau để hỗ trợ Cube hiện tại của bạn</t>
+          <t>Tiêu thụ Lượng Yêu Thích để hỗ trợ Khối Lập Phương hiện tại.</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tiêu hao lượng Popularity khác nhau để hỗ trợ Cube hiện tại của bạn</t>
+          <t>Tiêu thụ Lượng Yêu Thích để hỗ trợ Khối Lập Phương hiện tại.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem hướng dẫn chi tiết về Hỗ Trợ Cube.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hướng dẫn chi tiết về Hỗ Trợ Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem hướng dẫn chi tiết về Hỗ Trợ Cube.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hướng dẫn chi tiết về Hỗ Trợ Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem hướng dẫn chi tiết về Hỗ Trợ Cube.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hướng dẫn chi tiết về Hỗ Trợ Khối Lập Phương.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng Danh Vọng nếu Cube bạn ủng hộ giành vị trí đầu tiên!</t>
+          <t>Nhận phần thưởng Độ Nổi Tiếng nếu Khối Lập Phương bạn ủng hộ về nhất!</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng Danh Vọng nếu Cube bạn ủng hộ giành vị trí đầu tiên!</t>
+          <t>Nhận phần thưởng Độ Nổi Tiếng nếu Khối Lập Phương bạn ủng hộ về nhất!</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng Danh Vọng nếu Cube bạn ủng hộ giành vị trí đầu tiên!</t>
+          <t>Nhận phần thưởng Độ Nổi Tiếng nếu Khối Lập Phương bạn ủng hộ về nhất!</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
+          <t>Màn hình này hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
+          <t>Màn hình này hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
+          <t>Màn hình này hiển thị Bảng Xếp Hạng sau trận đấu. Bạn cũng có thể xem lại trận đấu tại đây.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Bạn có thể hỗ trợ Cube của mình cho trận đấu đã lên lịch tiếp theo tại đây.</t>
+          <t>Bạn có thể ủng hộ Khối Lập Phương của mình cho trận đấu đã lên lịch tiếp theo tại đây.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Bạn có thể hỗ trợ Cube của mình cho trận đấu đã lên lịch tiếp theo tại đây.</t>
+          <t>Bạn có thể ủng hộ Khối Lập Phương của mình cho trận đấu đã lên lịch tiếp theo tại đây.</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Bạn có thể hỗ trợ Cube của mình cho trận đấu đã lên lịch tiếp theo tại đây.</t>
+          <t>Bạn có thể ủng hộ Khối Lập Phương của mình cho trận đấu đã lên lịch tiếp theo tại đây.</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Race để kiểm tra tiến độ Race và xem lại replay.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút Race để kiểm tra tiến độ cuộc đua và xem lại các màn replay.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Bạn có thể kiểm tra Tiến trình Race và các Khối Lập phương còn tranh tài tại đây.</t>
+          <t>Cậu có thể kiểm tra Tiến trình Đua và các Khối Lập Phương còn tranh tài tại đây.</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Bạn có thể kiểm tra Tiến trình Race và các Khối Lập phương còn tranh tài tại đây.</t>
+          <t>Cậu có thể kiểm tra Tiến trình Đua và các Khối Lập Phương còn tranh tài tại đây.</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Bạn có thể kiểm tra Tiến trình Race và các Khối Lập phương còn tranh tài tại đây.</t>
+          <t>Cậu có thể kiểm tra Tiến trình Đua và các Khối Lập Phương còn tranh tài tại đây.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tất cả các giai đoạn Race và xem lại các trận đấu trước tại đây.</t>
+          <t>Bạn có thể xem tất cả các giai đoạn Race và xem lại các trận đấu trước tại đây</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tất cả các giai đoạn Race và xem lại các trận đấu trước tại đây.</t>
+          <t>Bạn có thể xem tất cả các giai đoạn Race và xem lại các trận đấu trước tại đây</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tất cả các giai đoạn Race và xem lại các trận đấu trước tại đây.</t>
+          <t>Bạn có thể xem tất cả các giai đoạn Race và xem lại các trận đấu trước tại đây</t>
         </is>
       </c>
     </row>
